--- a/Radinal_Excel_Portfolio_Fisheries.xlsx
+++ b/Radinal_Excel_Portfolio_Fisheries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ECA34E-21BA-4643-825C-2D979BDC5B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69621157-FBA4-4A14-9FF0-57F5F280D668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72C7BAF0-5E30-4EF3-9B04-943EEF12936B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{72C7BAF0-5E30-4EF3-9B04-943EEF12936B}"/>
   </bookViews>
   <sheets>
     <sheet name="ABOUT" sheetId="14" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5394" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5415" uniqueCount="359">
   <si>
     <t>Country (Name)</t>
   </si>
@@ -1102,28 +1102,162 @@
     <t>📊 INDONESIA FISHERIES ANALYSIS (2018-2022)</t>
   </si>
   <si>
-    <t>Author:</t>
+    <t>Last Update</t>
   </si>
   <si>
-    <t>Radinal</t>
+    <t>: https://www.linkedin.com/in/radinal-radinal-319b8972/</t>
   </si>
   <si>
-    <t>Role:</t>
+    <t>LinkedIn</t>
   </si>
   <si>
-    <t>Aspiring Data Analyst</t>
+    <t>Email</t>
   </si>
   <si>
-    <t>Email:</t>
+    <t>: radiradinal@outlook.com</t>
   </si>
   <si>
-    <t>radiradinal@outlook.com</t>
+    <t>Role</t>
   </si>
   <si>
-    <t>LinkedIn:</t>
+    <t>: Aspiring Data Analyst</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/radinal-radinal-319b8972/</t>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>: Radinal</t>
+  </si>
+  <si>
+    <t>2.596.481 Tonnes</t>
+  </si>
+  <si>
+    <t>from 2018-2022</t>
+  </si>
+  <si>
+    <t>#1 SCADS</t>
+  </si>
+  <si>
+    <t>#1 SNAPPERS</t>
+  </si>
+  <si>
+    <t>USD$ 5 MILLION</t>
+  </si>
+  <si>
+    <t>#1 GROUPERS</t>
+  </si>
+  <si>
+    <t>SEABASSES</t>
+  </si>
+  <si>
+    <t>CONCLUSION</t>
+  </si>
+  <si>
+    <t>*Findings are based on 2018–2022 FAO data and local market prices.
+*Further analysis needed to establish causal links between fishing effort, environmental factors, and stock decline.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="4"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Snappers </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="1"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">generate the best economic value ($5.03M), but </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="4"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t>Groupers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="1"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the second place declining fastest (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t>-79%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="1"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t>) threatening future revenue.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> :   May 25th 2026</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="4"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scads</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="1"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have the highest catch volume (2.6M tonnes), making them the backbone of Indonesia's bulk fishery output.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>High volume ≠ high revenue. Species with moderate catch but premium prices (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="4"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t>Snappers, Blue Swimming Crab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="26"/>
+        <color theme="1"/>
+        <rFont val="Agency FB"/>
+        <family val="2"/>
+      </rPr>
+      <t>) often drives revenue more than bulk catch</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1134,7 +1268,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1189,14 +1323,44 @@
       <family val="3"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Agency FB"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Agency FB"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="4"/>
+      <name val="Agency FB"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Agency FB"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1207,6 +1371,18 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1237,7 +1413,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -1265,21 +1441,54 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="12"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1514,6 +1723,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1526,897 +1740,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Radinal_Excel_Portfolio_Fisheries.xlsx]Top 5 Species by Catch!PivotTable1</c:name>
-    <c:fmtId val="2"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>HIGHEST</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> CATCH</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:numFmt formatCode="#,##0" sourceLinked="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Top 5 Species by Catch'!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:numFmt formatCode="#,##0" sourceLinked="0"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Top 5 Species by Catch'!$A$2:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Scads nei</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Marine fishes nei</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Skipjack tuna</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Yellowfin tuna</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Indian mackerels nei</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Top 5 Species by Catch'!$B$2:$B$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2596480.5599999996</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1993648.16</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1982631.79</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1318443.27</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1099882.18</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5012-405E-B753-CCA100CB81C5}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="100"/>
-        <c:overlap val="-24"/>
-        <c:axId val="125290608"/>
-        <c:axId val="125291024"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="125290608"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="125291024"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="125291024"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>TONNES</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="125290608"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2460,14 +1783,23 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>BEST REVENUE: VOLUME</a:t>
+              <a:rPr lang="en-US" sz="2400"/>
+              <a:t>BEST REVENUE</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" b="0"/>
+              <a:t>VOLUME</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> * DECENT PRICE</a:t>
+              <a:rPr lang="en-US" sz="1200" b="0" baseline="0"/>
+              <a:t> x DECENT PRICE</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-US" sz="1200" b="0"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3083,7 +2415,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>pRICE iN bILLIONS</a:t>
+                  <a:t>pRICE iN mILLIONS</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3227,7 +2559,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3252,17 +2584,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
                 </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="2000"/>
               <a:t>Declining Species</a:t>
             </a:r>
           </a:p>
@@ -3281,10 +2622,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -3299,72 +2649,55 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="88000"/>
-            </a:schemeClr>
-          </a:solidFill>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
           <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
-          <a:effectLst/>
-          <a:scene3d>
-            <a:camera prst="orthographicFront"/>
-            <a:lightRig rig="threePt" dir="t"/>
-          </a:scene3d>
-          <a:sp3d prstMaterial="flat">
-            <a:contourClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:contourClr>
-          </a:sp3d>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:numFmt formatCode="#,##0" sourceLinked="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4472C4">
-                <a:alpha val="30000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln>
-              <a:solidFill>
-                <a:sysClr val="window" lastClr="FFFFFF">
-                  <a:alpha val="50000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:round/>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-                <a:prstClr val="black">
-                  <a:alpha val="40000"/>
-                </a:prstClr>
-              </a:outerShdw>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
           <c:txPr>
             <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -3373,9 +2706,11 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1"/>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3385,6 +2720,7 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -3399,89 +2735,55 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="88000"/>
-            </a:schemeClr>
-          </a:solidFill>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
           <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
-          <a:effectLst/>
-          <a:scene3d>
-            <a:camera prst="orthographicFront"/>
-            <a:lightRig rig="threePt" dir="t"/>
-          </a:scene3d>
-          <a:sp3d prstMaterial="flat">
-            <a:contourClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:contourClr>
-          </a:sp3d>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="88000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:scene3d>
-            <a:camera prst="orthographicFront"/>
-            <a:lightRig rig="threePt" dir="t"/>
-          </a:scene3d>
-          <a:sp3d prstMaterial="flat">
-            <a:contourClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="8.8889107611548557E-2"/>
-              <c:y val="0"/>
-            </c:manualLayout>
-          </c:layout>
+          <c:numFmt formatCode="#,##0" sourceLinked="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4472C4">
-                <a:alpha val="30000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln>
-              <a:solidFill>
-                <a:sysClr val="window" lastClr="FFFFFF">
-                  <a:alpha val="50000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:round/>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-                <a:prstClr val="black">
-                  <a:alpha val="40000"/>
-                </a:prstClr>
-              </a:outerShdw>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
           <c:txPr>
             <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -3490,9 +2792,11 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1"/>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3502,6 +2806,93 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -3516,57 +2907,55 @@
       <c:pivotFmt>
         <c:idx val="3"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="88000"/>
-            </a:schemeClr>
-          </a:solidFill>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
           <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
-          <a:effectLst/>
-          <a:scene3d>
-            <a:camera prst="orthographicFront"/>
-            <a:lightRig rig="threePt" dir="t"/>
-          </a:scene3d>
-          <a:sp3d prstMaterial="flat">
-            <a:contourClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:contourClr>
-          </a:sp3d>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:numFmt formatCode="#,##0" sourceLinked="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4472C4">
-                <a:alpha val="30000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln>
-              <a:solidFill>
-                <a:sysClr val="window" lastClr="FFFFFF">
-                  <a:alpha val="50000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:round/>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-                <a:prstClr val="black">
-                  <a:alpha val="40000"/>
-                </a:prstClr>
-              </a:outerShdw>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
           <c:txPr>
             <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -3575,9 +2964,11 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1"/>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3587,267 +2978,7 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="88000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:scene3d>
-            <a:camera prst="orthographicFront"/>
-            <a:lightRig rig="threePt" dir="t"/>
-          </a:scene3d>
-          <a:sp3d prstMaterial="flat">
-            <a:contourClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="8.8889107611548557E-2"/>
-              <c:y val="0"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4472C4">
-                <a:alpha val="30000"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:sysClr val="window" lastClr="FFFFFF">
-                  <a:alpha val="50000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-                <a:prstClr val="black">
-                  <a:alpha val="40000"/>
-                </a:prstClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="88000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:scene3d>
-            <a:camera prst="orthographicFront"/>
-            <a:lightRig rig="threePt" dir="t"/>
-          </a:scene3d>
-          <a:sp3d prstMaterial="flat">
-            <a:contourClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4472C4">
-                <a:alpha val="30000"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:sysClr val="window" lastClr="FFFFFF">
-                  <a:alpha val="50000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-                <a:prstClr val="black">
-                  <a:alpha val="40000"/>
-                </a:prstClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="88000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-          <a:scene3d>
-            <a:camera prst="orthographicFront"/>
-            <a:lightRig rig="threePt" dir="t"/>
-          </a:scene3d>
-          <a:sp3d prstMaterial="flat">
-            <a:contourClr>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:contourClr>
-          </a:sp3d>
-        </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="8.8889107611548557E-2"/>
-              <c:y val="0"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4472C4">
-                <a:alpha val="30000"/>
-              </a:srgbClr>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:sysClr val="window" lastClr="FFFFFF">
-                  <a:alpha val="50000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-                <a:prstClr val="black">
-                  <a:alpha val="40000"/>
-                </a:prstClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -3860,64 +2991,10 @@
         </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
-    <c:view3D>
-      <c:rotX val="15"/>
-      <c:rotY val="20"/>
-      <c:depthPercent val="100"/>
-      <c:rAngAx val="1"/>
-    </c:view3D>
-    <c:floor>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="75000"/>
-            <a:alpha val="27000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:floor>
-    <c:sideWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:sideWall>
-    <c:backWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:backWall>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.1736111111111111"/>
-          <c:y val="0.27819225721784779"/>
-          <c:w val="0.79305555555555551"/>
-          <c:h val="0.68014107611548558"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:bar3DChart>
-        <c:barDir val="bar"/>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -3935,111 +3012,52 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="88000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst/>
-            <a:scene3d>
-              <a:camera prst="orthographicFront"/>
-              <a:lightRig rig="threePt" dir="t"/>
-            </a:scene3d>
-            <a:sp3d prstMaterial="flat">
-              <a:contourClr>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:contourClr>
-            </a:sp3d>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0" sourceLinked="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:alpha val="88000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:noFill/>
               <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="threePt" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="flat">
-                <a:contourClr>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:contourClr>
-              </a:sp3d>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-A10F-4C1D-B178-FDCDB32E6142}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="8.8889107611548557E-2"/>
-                  <c:y val="0"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-A10F-4C1D-B178-FDCDB32E6142}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4472C4">
-                  <a:alpha val="30000"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:sysClr val="window" lastClr="FFFFFF">
-                    <a:alpha val="50000"/>
-                  </a:sysClr>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
             </c:spPr>
             <c:txPr>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -4048,9 +3066,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1"/>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -4060,6 +3080,7 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -4075,10 +3096,10 @@
                     <a:ln w="9525">
                       <a:solidFill>
                         <a:schemeClr val="lt1">
-                          <a:lumMod val="50000"/>
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -4135,11 +3156,12 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A10F-4C1D-B178-FDCDB32E6142}"/>
+              <c16:uniqueId val="{00000003-792E-476E-8F63-883CBC44C681}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -4147,20 +3169,793 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="84"/>
-        <c:gapDepth val="53"/>
-        <c:shape val="box"/>
-        <c:axId val="376879584"/>
-        <c:axId val="376884576"/>
-        <c:axId val="0"/>
-      </c:bar3DChart>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="263690576"/>
+        <c:axId val="263692656"/>
+      </c:barChart>
       <c:catAx>
-        <c:axId val="376879584"/>
+        <c:axId val="263690576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="263692656"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="263692656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="263690576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:clrMapOvr bg1="lt1" tx1="dk1" bg2="lt2" tx2="dk2" accent1="accent1" accent2="accent2" accent3="accent3" accent4="accent4" accent5="accent5" accent6="accent6" hlink="hlink" folHlink="folHlink"/>
+  <c:pivotSource>
+    <c:name>[Radinal_Excel_Portfolio_Fisheries.xlsx]Top 5 Species by Catch!PivotTable1</c:name>
+    <c:fmtId val="14"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000"/>
+              <a:t>HIGHEST</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" baseline="0"/>
+              <a:t> CATCH</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="2000"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Top 5 Species by Catch'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Top 5 Species by Catch'!$A$2:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Scads nei</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Marine fishes nei</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Skipjack tuna</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Yellowfin tuna</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Indian mackerels nei</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Top 5 Species by Catch'!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2596480.5599999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1993648.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1982631.79</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1318443.27</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1099882.18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-28DD-48B0-885B-03B61035E641}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="263690576"/>
+        <c:axId val="263692656"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="263690576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="263692656"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="263692656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -4180,7 +3975,7 @@
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
-                    <a:lumMod val="75000"/>
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -4191,25 +3986,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="376884576"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="376884576"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="376879584"/>
+        <c:crossAx val="263690576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4222,7 +3999,7 @@
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4233,19 +4010,28 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </a:solidFill>
-    <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:tint val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -5716,6 +5502,32 @@
             <c:idx val="4"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="88000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:contourClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000003-7537-47A6-93F2-8D1FBFF2E2B8}"/>
@@ -7240,17 +7052,17 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="291">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -7258,9 +7070,20 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea>
@@ -7268,163 +7091,94 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:tint val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
     <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="30000"/>
-        </a:schemeClr>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-      <a:effectLst>
-        <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
     </cs:spPr>
-    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="30000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-      <a:effectLst>
-        <a:outerShdw blurRad="63500" dist="88900" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="88000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="88000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-      <a:scene3d>
-        <a:camera prst="orthographicFront"/>
-        <a:lightRig rig="threePt" dir="t"/>
-      </a:scene3d>
-      <a:sp3d prstMaterial="flat"/>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -7433,25 +7187,22 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
@@ -7460,10 +7211,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -7480,15 +7231,15 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -7505,17 +7256,17 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -7524,16 +7275,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -7542,13 +7294,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7560,32 +7312,25 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg2">
-          <a:lumMod val="75000"/>
-          <a:alpha val="27000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:sp3d/>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMajor>
@@ -7594,13 +7339,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln>
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="40000"/>
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -7611,16 +7357,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -7629,16 +7376,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -7648,7 +7395,7 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -7658,7 +7405,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -7666,7 +7413,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -7675,9 +7422,20 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -7685,13 +7443,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7703,9 +7462,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1800" b="0" kern="1200" cap="all" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -7714,14 +7483,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="rnd">
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
@@ -7732,7 +7499,7 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -7742,21 +7509,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -7766,7 +7531,7 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -7776,11 +7541,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:sp3d/>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -9327,23 +9089,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>43543</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>2719</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>40822</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F3E0454-10D6-40C7-AC05-40BBD8CB2BF8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF698531-F37A-486A-83B9-7A881E9D3488}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9365,23 +9127,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>174171</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>47622</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>13608</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>176891</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF698531-F37A-486A-83B9-7A881E9D3488}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED02A069-AB92-4A02-9B35-9B81C6E88271}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9403,23 +9165,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>27214</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1361</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>503465</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="11" name="Chart 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED02A069-AB92-4A02-9B35-9B81C6E88271}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{247AE8B1-C4B3-4C7F-B41E-66ACFC9AED7A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9437,6 +9199,291 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>189331</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>164502</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>397499</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>67106</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Arrow: Down 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{191E2733-1366-B91D-FBEB-E33DF1FA8ED1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="2632485">
+          <a:off x="10562056" y="926502"/>
+          <a:ext cx="208168" cy="283604"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>598714</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>326571</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Flowchart: Connector 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE806FFD-3DE3-5C6E-0693-4222A81A1B72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1836964" y="6830786"/>
+          <a:ext cx="952500" cy="870857"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="4400">
+              <a:latin typeface="Agency FB" panose="020B0503020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:latin typeface="Agency FB" panose="020B0503020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>435428</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Flowchart: Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A35A412-51E6-487B-835F-4D9861CD49AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5728607" y="6830786"/>
+          <a:ext cx="952500" cy="870857"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="0" lang="en-US" sz="4400" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:prstClr val="white"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Agency FB" panose="020B0503020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>149679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>530679</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>68036</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Flowchart: Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B18A44C5-E63C-49EF-ACCB-5D5203291A0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9593036" y="6817179"/>
+          <a:ext cx="952500" cy="870857"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="0" lang="en-US" sz="4400" b="0" i="0" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:prstClr val="white"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Agency FB" panose="020B0503020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -9487,16 +9534,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1819275</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>42862</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1800225</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10102,7 +10149,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DCDC92F4-E6B5-48CC-95C3-8A2506C9295E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DCDC92F4-E6B5-48CC-95C3-8A2506C9295E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
   <location ref="A1:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -10165,7 +10212,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="2" format="3" series="1">
+    <chartFormat chart="4" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -10174,7 +10221,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
+    <chartFormat chart="14" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -10385,7 +10432,7 @@
       </pivotArea>
     </format>
   </formats>
-  <chartFormats count="7">
+  <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -10440,23 +10487,11 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="2" format="5" series="1">
+    <chartFormat chart="2" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="6"/>
           </reference>
         </references>
       </pivotArea>
@@ -10834,10 +10869,299 @@
 </a:theme>
 </file>
 
+<file path=xl/theme/themeOverride1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:themeOverride xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <a:clrScheme name="Office">
+    <a:dk1>
+      <a:sysClr val="windowText" lastClr="000000"/>
+    </a:dk1>
+    <a:lt1>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:lt1>
+    <a:dk2>
+      <a:srgbClr val="44546A"/>
+    </a:dk2>
+    <a:lt2>
+      <a:srgbClr val="E7E6E6"/>
+    </a:lt2>
+    <a:accent1>
+      <a:srgbClr val="4472C4"/>
+    </a:accent1>
+    <a:accent2>
+      <a:srgbClr val="ED7D31"/>
+    </a:accent2>
+    <a:accent3>
+      <a:srgbClr val="A5A5A5"/>
+    </a:accent3>
+    <a:accent4>
+      <a:srgbClr val="FFC000"/>
+    </a:accent4>
+    <a:accent5>
+      <a:srgbClr val="5B9BD5"/>
+    </a:accent5>
+    <a:accent6>
+      <a:srgbClr val="70AD47"/>
+    </a:accent6>
+    <a:hlink>
+      <a:srgbClr val="0563C1"/>
+    </a:hlink>
+    <a:folHlink>
+      <a:srgbClr val="954F72"/>
+    </a:folHlink>
+  </a:clrScheme>
+  <a:fontScheme name="Office">
+    <a:majorFont>
+      <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="游ゴシック Light"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="等线 Light"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Times New Roman"/>
+      <a:font script="Hebr" typeface="Times New Roman"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="MoolBoran"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Times New Roman"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+      <a:font script="Armn" typeface="Arial"/>
+      <a:font script="Bugi" typeface="Leelawadee UI"/>
+      <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+      <a:font script="Java" typeface="Javanese Text"/>
+      <a:font script="Lisu" typeface="Segoe UI"/>
+      <a:font script="Mymr" typeface="Myanmar Text"/>
+      <a:font script="Nkoo" typeface="Ebrima"/>
+      <a:font script="Olck" typeface="Nirmala UI"/>
+      <a:font script="Osma" typeface="Ebrima"/>
+      <a:font script="Phag" typeface="Phagspa"/>
+      <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+      <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+      <a:font script="Syre" typeface="Estrangelo Edessa"/>
+      <a:font script="Sora" typeface="Nirmala UI"/>
+      <a:font script="Tale" typeface="Microsoft Tai Le"/>
+      <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+      <a:font script="Tfng" typeface="Ebrima"/>
+    </a:majorFont>
+    <a:minorFont>
+      <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+      <a:ea typeface=""/>
+      <a:cs typeface=""/>
+      <a:font script="Jpan" typeface="游ゴシック"/>
+      <a:font script="Hang" typeface="맑은 고딕"/>
+      <a:font script="Hans" typeface="等线"/>
+      <a:font script="Hant" typeface="新細明體"/>
+      <a:font script="Arab" typeface="Arial"/>
+      <a:font script="Hebr" typeface="Arial"/>
+      <a:font script="Thai" typeface="Tahoma"/>
+      <a:font script="Ethi" typeface="Nyala"/>
+      <a:font script="Beng" typeface="Vrinda"/>
+      <a:font script="Gujr" typeface="Shruti"/>
+      <a:font script="Khmr" typeface="DaunPenh"/>
+      <a:font script="Knda" typeface="Tunga"/>
+      <a:font script="Guru" typeface="Raavi"/>
+      <a:font script="Cans" typeface="Euphemia"/>
+      <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+      <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+      <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+      <a:font script="Thaa" typeface="MV Boli"/>
+      <a:font script="Deva" typeface="Mangal"/>
+      <a:font script="Telu" typeface="Gautami"/>
+      <a:font script="Taml" typeface="Latha"/>
+      <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+      <a:font script="Orya" typeface="Kalinga"/>
+      <a:font script="Mlym" typeface="Kartika"/>
+      <a:font script="Laoo" typeface="DokChampa"/>
+      <a:font script="Sinh" typeface="Iskoola Pota"/>
+      <a:font script="Mong" typeface="Mongolian Baiti"/>
+      <a:font script="Viet" typeface="Arial"/>
+      <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      <a:font script="Geor" typeface="Sylfaen"/>
+      <a:font script="Armn" typeface="Arial"/>
+      <a:font script="Bugi" typeface="Leelawadee UI"/>
+      <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+      <a:font script="Java" typeface="Javanese Text"/>
+      <a:font script="Lisu" typeface="Segoe UI"/>
+      <a:font script="Mymr" typeface="Myanmar Text"/>
+      <a:font script="Nkoo" typeface="Ebrima"/>
+      <a:font script="Olck" typeface="Nirmala UI"/>
+      <a:font script="Osma" typeface="Ebrima"/>
+      <a:font script="Phag" typeface="Phagspa"/>
+      <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+      <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+      <a:font script="Syre" typeface="Estrangelo Edessa"/>
+      <a:font script="Sora" typeface="Nirmala UI"/>
+      <a:font script="Tale" typeface="Microsoft Tai Le"/>
+      <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+      <a:font script="Tfng" typeface="Ebrima"/>
+    </a:minorFont>
+  </a:fontScheme>
+  <a:fmtScheme name="Office">
+    <a:fillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="110000"/>
+              <a:satMod val="105000"/>
+              <a:tint val="67000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="50000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="105000"/>
+              <a:satMod val="103000"/>
+              <a:tint val="73000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="105000"/>
+              <a:satMod val="109000"/>
+              <a:tint val="81000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:satMod val="103000"/>
+              <a:lumMod val="102000"/>
+              <a:tint val="94000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="50000">
+            <a:schemeClr val="phClr">
+              <a:satMod val="110000"/>
+              <a:lumMod val="100000"/>
+              <a:shade val="100000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="99000"/>
+              <a:satMod val="120000"/>
+              <a:shade val="78000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </a:fillStyleLst>
+    <a:lnStyleLst>
+      <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="solid"/>
+        <a:miter lim="800000"/>
+      </a:ln>
+    </a:lnStyleLst>
+    <a:effectStyleLst>
+      <a:effectStyle>
+        <a:effectLst/>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst/>
+      </a:effectStyle>
+      <a:effectStyle>
+        <a:effectLst>
+          <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="63000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </a:effectStyle>
+    </a:effectStyleLst>
+    <a:bgFillStyleLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:tint val="95000"/>
+          <a:satMod val="170000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:tint val="93000"/>
+              <a:satMod val="150000"/>
+              <a:shade val="98000"/>
+              <a:lumMod val="102000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="50000">
+            <a:schemeClr val="phClr">
+              <a:tint val="98000"/>
+              <a:satMod val="130000"/>
+              <a:shade val="90000"/>
+              <a:lumMod val="103000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:shade val="63000"/>
+              <a:satMod val="120000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </a:bgFillStyleLst>
+  </a:fmtScheme>
+</a:themeOverride>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38421285-B36C-4DB0-A224-360A6F001859}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
@@ -10849,65 +11173,73 @@
       <c r="E1" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="B7" t="s">
+        <v>356</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LdKsWAR0JLv+rDwWcGw9K6PpsEIk9DmdWGKrEtUGU37N8+MNeSEFmPsHae/C44xGqXu2E+7lGEBbcE2SC+uHgw==" saltValue="hVtoivx2oJoiLI2w4ohDnw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xYAOYfHxjO7lIhumuY3jIq5juvPiU4LZwyT0VaWF5TMEiNcCRk7F6ffjpyKgkoglYn0U3dq78OOWXdqHwuQtEQ==" saltValue="qhkPTEBMAxWjmC2+f9Q3GA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B4:D4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{2ED9ADFF-AD38-4D80-9C65-BEED201B0CB2}"/>
+    <hyperlink ref="B5" r:id="rId1" display="radiradinal@outlook.com" xr:uid="{2ED9ADFF-AD38-4D80-9C65-BEED201B0CB2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -10916,14 +11248,14 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C6D721-FCBD-4FFB-AE77-C520A12AC82C}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>331</v>
       </c>
@@ -10931,7 +11263,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>121</v>
       </c>
@@ -10939,7 +11271,7 @@
         <v>-0.79215006173612945</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>103</v>
       </c>
@@ -10947,7 +11279,7 @@
         <v>-0.48297090240600954</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>269</v>
       </c>
@@ -10955,31 +11287,81 @@
         <v>-0.4140832544440684</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>140</v>
       </c>
       <c r="B5" s="14">
         <v>-0.37990425845035247</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G5" s="29">
+        <v>-0.79</v>
+      </c>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>114</v>
       </c>
       <c r="B6" s="14">
         <v>-0.16567750379395754</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>332</v>
       </c>
       <c r="B7">
         <v>-2.2347859808305173</v>
       </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G8" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="G5:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G9:J10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
@@ -48442,72 +48824,708 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08C9DB4-03DD-4108-A711-15770AE6D264}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:X54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="3" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="1.5703125" customWidth="1"/>
+    <col min="15" max="15" width="1.42578125" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-    </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="5"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+    </row>
+    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+    </row>
+    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+    </row>
+    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25"/>
+    </row>
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+      <c r="C5" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="J5" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="Q5" s="31">
+        <v>-0.79</v>
+      </c>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+    </row>
+    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+    </row>
+    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="27"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="27"/>
+      <c r="C9" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="J9" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="Q9" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="23"/>
+    </row>
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="23"/>
+    </row>
+    <row r="33" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="21"/>
+    </row>
+    <row r="34" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21"/>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
+      <c r="R34" s="21"/>
+      <c r="S34" s="21"/>
+      <c r="T34" s="21"/>
+      <c r="U34" s="21"/>
+    </row>
+    <row r="35" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
+    </row>
+    <row r="36" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="33"/>
+    </row>
+    <row r="37" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="33"/>
+      <c r="T37" s="33"/>
+      <c r="U37" s="33"/>
+    </row>
+    <row r="38" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="33"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
+      <c r="S38" s="33"/>
+      <c r="T38" s="33"/>
+      <c r="U38" s="33"/>
+    </row>
+    <row r="39" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="33"/>
+    </row>
+    <row r="40" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="33"/>
+      <c r="M40" s="33"/>
+      <c r="N40" s="33"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="33"/>
+      <c r="T40" s="33"/>
+      <c r="U40" s="33"/>
+    </row>
+    <row r="41" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="33"/>
+      <c r="N41" s="33"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="33"/>
+    </row>
+    <row r="42" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33"/>
+      <c r="U42" s="33"/>
+    </row>
+    <row r="43" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="33"/>
+      <c r="M43" s="33"/>
+      <c r="N43" s="33"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="33"/>
+      <c r="S43" s="33"/>
+      <c r="T43" s="33"/>
+      <c r="U43" s="33"/>
+    </row>
+    <row r="44" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="33"/>
+      <c r="N44" s="33"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="33"/>
+    </row>
+    <row r="45" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="33"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="33"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="33"/>
+    </row>
+    <row r="46" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+    </row>
+    <row r="47" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+    </row>
+    <row r="48" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="33"/>
+    </row>
+    <row r="49" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
+      <c r="M49" s="33"/>
+      <c r="N49" s="33"/>
+      <c r="O49" s="24"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="33"/>
+      <c r="S49" s="33"/>
+      <c r="T49" s="33"/>
+      <c r="U49" s="33"/>
+    </row>
+    <row r="50" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
+      <c r="M50" s="33"/>
+      <c r="N50" s="33"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="33"/>
+      <c r="Q50" s="33"/>
+      <c r="R50" s="33"/>
+      <c r="S50" s="33"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="33"/>
+    </row>
+    <row r="51" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+      <c r="M51" s="33"/>
+      <c r="N51" s="33"/>
+      <c r="O51" s="24"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="33"/>
+      <c r="S51" s="33"/>
+      <c r="T51" s="33"/>
+      <c r="U51" s="33"/>
+    </row>
+    <row r="52" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
+      <c r="M52" s="33"/>
+      <c r="N52" s="33"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="33"/>
+      <c r="Q52" s="33"/>
+      <c r="R52" s="33"/>
+      <c r="S52" s="33"/>
+      <c r="T52" s="33"/>
+      <c r="U52" s="33"/>
+    </row>
+    <row r="53" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="34"/>
+      <c r="M53" s="34"/>
+      <c r="N53" s="34"/>
+      <c r="O53" s="34"/>
+      <c r="P53" s="34"/>
+      <c r="Q53" s="34"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="34"/>
+      <c r="T53" s="34"/>
+      <c r="U53" s="34"/>
+    </row>
+    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="34"/>
+      <c r="M54" s="34"/>
+      <c r="N54" s="34"/>
+      <c r="O54" s="34"/>
+      <c r="P54" s="34"/>
+      <c r="Q54" s="34"/>
+      <c r="R54" s="34"/>
+      <c r="S54" s="34"/>
+      <c r="T54" s="34"/>
+      <c r="U54" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A1:N2"/>
+  <mergeCells count="16">
+    <mergeCell ref="B53:U54"/>
+    <mergeCell ref="A1:U2"/>
+    <mergeCell ref="B33:U35"/>
+    <mergeCell ref="B36:G52"/>
+    <mergeCell ref="I36:N52"/>
+    <mergeCell ref="P36:U52"/>
+    <mergeCell ref="C5:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F11"/>
+    <mergeCell ref="J5:M7"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J9:M11"/>
+    <mergeCell ref="Q5:T7"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="Q9:T10"/>
+    <mergeCell ref="Q11:T11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -48516,14 +49534,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE98A0A5-3FFD-4FF3-96AD-E449681F6766}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>331</v>
       </c>
@@ -48531,7 +49549,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>206</v>
       </c>
@@ -48539,7 +49557,7 @@
         <v>2596480.5599999996</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>163</v>
       </c>
@@ -48547,7 +49565,7 @@
         <v>1993648.16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>223</v>
       </c>
@@ -48555,31 +49573,78 @@
         <v>1982631.79</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>269</v>
       </c>
       <c r="B5">
         <v>1318443.27</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="H5" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>140</v>
       </c>
       <c r="B6">
         <v>1099882.18</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>332</v>
       </c>
       <c r="B7">
         <v>8991085.959999999</v>
       </c>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H8" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H9" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H5:K7"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="H9:K11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -48587,14 +49652,14 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC64460-A752-4855-B961-7C4B175D0A26}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>331</v>
       </c>
@@ -48602,7 +49667,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>228</v>
       </c>
@@ -48610,7 +49675,7 @@
         <v>5.0291029250000001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>121</v>
       </c>
@@ -48618,39 +49683,84 @@
         <v>4.6858550999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>55</v>
       </c>
       <c r="B4">
         <v>3.7495050449999994</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F4" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>173</v>
       </c>
       <c r="B5">
         <v>3.3451382299999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>229</v>
       </c>
       <c r="B6">
         <v>3.2964413100000005</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>332</v>
       </c>
       <c r="B7">
         <v>20.106042609999996</v>
       </c>
+      <c r="F7" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F8" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F4:I6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
